--- a/tests/market/fixtures/mpcvoting_sample.xlsx
+++ b/tests/market/fixtures/mpcvoting_sample.xlsx
@@ -416,211 +416,1798 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:GI27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>MPC voting record: Bank Rate decisions</t>
-        </is>
-      </c>
-    </row>
+    <row r="1"/>
     <row r="2">
       <c r="D2" t="inlineStr">
         <is>
+          <t>Monetary Policy Committee voting history - Bank Rate</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="C4" t="inlineStr">
+        <is>
           <t>Current members</t>
         </is>
       </c>
-    </row>
-    <row r="3">
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Member A</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Member B</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Member C</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Member D</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Member E</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Andrew Bailey</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Sarah Breeden</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Swati Dhingra</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Megan Greene</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Clare Lombardelli</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Catherine L Mann</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Huw Pill</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Dave Ramsden</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Alan Taylor</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
         <is>
           <t>Past members</t>
         </is>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>notes</t>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Christopher Allsopp</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Kate Barker</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Charles Bean</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Marian Bell</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Tim Besley</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>David Blanchflower</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Ben Broadbent</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Alan Budd</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Willem Buiter</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Mark Carney</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>David Clementi</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Jon Cunliffe</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Spencer Dale</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Howard Davies</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Paul Fisher</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Kristin Forbes</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Eddie George</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>John Gieve</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Charles Goodhart</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Andrew
+Haldane</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Jonathan Haskel</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Charlotte
+Hogg</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>DeAnne Julius</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Mervyn King</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>Richard Lambert</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Andrew Large</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>Rachel Lomax</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Ian
+McCafferty</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>David Miles</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>Stephen Nickell</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>Ian Plenderleith</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>Adam Posen</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>Michael
+Saunders</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>Andrew Sentance</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>Nemat Shafik</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Silvana Tenreyro</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Paul Tucker</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>John Vickers</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>Gertjan
+Vlieghe</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>Sushil Wadhwani</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>David Walton</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>Martin Weale</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>notes</t>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>First vote:
+19 Mar 20</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">First vote:
+2 Nov 23 </t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>First vote:
+22 Sep 22</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>First vote:
+3 Aug 23</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>First vote:
+1 Aug 24</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>First vote:
+23 Sep 21</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>First vote:
+23 Sep 21</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>First vote:
+14 Sep 17</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>First vote:
+19 Sep 24</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Last vote:
+8 May 03</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Last vote:
+10 May 10</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Last vote:
+5 Jun 14</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Last vote:
+9 Jun 05</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Last vote:
+6 Aug 09</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Last vote:
+7 May 09</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Last vote:
+20 Jun 24</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Last vote:
+6 May 99</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Last vote:
+4 May 00</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Last vote:
+11 Mar 20</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Last vote:
+1 Aug 02</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Last vote:
+21 Sept 23</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Last vote:
+8 May 14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Last vote:
+10 Jul 97</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Last vote:
+10 Jul 14</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Last vote:
+15 Jun 17</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Last vote:
+5 Jun 03</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Last vote:
+5 Feb 09</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Last vote:
+4 May 00</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Last vote:
+24 Jun 21</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Last vote:
+1 Aug 24</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Last vote:
+16 Mar 17</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>Last vote:
+10 May 01</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Last vote:
+6 Jun 13</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Last vote:
+9 Mar 06</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Last vote:
+12 Jan 06</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>Last vote:
+5 Jun 08</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Last vote:
+2 Aug 18  </t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>Last vote:
+6 Aug 15</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>Last vote:
+4 May 06</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>Last vote:
+9 May 02</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>Last vote:
+2 Aug 12</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>Last vote:
+4 Aug 22</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Last vote:
+5 May 11</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>Last vote:
+2 Feb 17</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Last vote:
+22 June 23</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Last vote:
+9 Oct 13</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Last vote:
+7 Sep 00</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>Last vote:
+5 Aug 21</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>Last vote:
+9 May 02</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>Last vote:
+8 Jun 06</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>Last vote:
+4 Aug 16</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Voted to increase</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2</v>
+      </c>
+      <c r="G6" t="n">
+        <v>7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>20</v>
+      </c>
+      <c r="J6" t="n">
+        <v>18</v>
+      </c>
+      <c r="K6" t="n">
+        <v>16</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>11</v>
+      </c>
+      <c r="P6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>4</v>
+      </c>
+      <c r="R6" t="n">
+        <v>10</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>16</v>
+      </c>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>17</v>
+      </c>
+      <c r="W6" t="n">
+        <v>2</v>
+      </c>
+      <c r="X6" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>20</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>9</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>13</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>10</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>3</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Voted to maintain</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>33</v>
+      </c>
+      <c r="E7" t="n">
+        <v>16</v>
+      </c>
+      <c r="F7" t="n">
+        <v>14</v>
+      </c>
+      <c r="G7" t="n">
+        <v>16</v>
+      </c>
+      <c r="H7" t="n">
+        <v>14</v>
+      </c>
+      <c r="I7" t="n">
+        <v>20</v>
+      </c>
+      <c r="J7" t="n">
+        <v>21</v>
+      </c>
+      <c r="K7" t="n">
+        <v>45</v>
+      </c>
+      <c r="L7" t="n">
+        <v>7</v>
+      </c>
+      <c r="N7" t="n">
+        <v>19</v>
+      </c>
+      <c r="O7" t="n">
+        <v>78</v>
+      </c>
+      <c r="P7" t="n">
+        <v>136</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>26</v>
+      </c>
+      <c r="R7" t="n">
+        <v>18</v>
+      </c>
+      <c r="S7" t="n">
+        <v>16</v>
+      </c>
+      <c r="T7" t="n">
+        <v>109</v>
+      </c>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="n">
+        <v>9</v>
+      </c>
+      <c r="W7" t="n">
+        <v>63</v>
+      </c>
+      <c r="X7" t="n">
+        <v>39</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>59</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>64</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>29</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>17</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>62</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>25</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>141</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>27</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>50</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>44</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>41</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>39</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>30</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>28</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>39</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>114</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>11</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>48</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>8</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Voted to reduce</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>7</v>
+      </c>
+      <c r="E8" t="n">
+        <v>8</v>
+      </c>
+      <c r="F8" t="n">
+        <v>17</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
+      <c r="H8" t="n">
+        <v>4</v>
+      </c>
+      <c r="I8" t="n">
+        <v>1</v>
+      </c>
+      <c r="J8" t="n">
+        <v>2</v>
+      </c>
+      <c r="K8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L8" t="n">
+        <v>10</v>
+      </c>
+      <c r="N8" t="n">
+        <v>18</v>
+      </c>
+      <c r="O8" t="n">
+        <v>20</v>
+      </c>
+      <c r="P8" t="n">
+        <v>22</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>6</v>
+      </c>
+      <c r="R8" t="n">
+        <v>8</v>
+      </c>
+      <c r="S8" t="n">
+        <v>19</v>
+      </c>
+      <c r="T8" t="n">
+        <v>3</v>
+      </c>
+      <c r="U8" t="n">
+        <v>6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>10</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>3</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>6</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>2</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>10</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>7</v>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>16</v>
+      </c>
+      <c r="BB8" t="n">
+        <v>2</v>
+      </c>
+      <c r="BC8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>notes</t>
-        </is>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Meetings</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>54</v>
+      </c>
+      <c r="E9" t="n">
+        <v>24</v>
+      </c>
+      <c r="F9" t="n">
+        <v>33</v>
+      </c>
+      <c r="G9" t="n">
+        <v>26</v>
+      </c>
+      <c r="H9" t="n">
+        <v>18</v>
+      </c>
+      <c r="I9" t="n">
+        <v>41</v>
+      </c>
+      <c r="J9" t="n">
+        <v>41</v>
+      </c>
+      <c r="K9" t="n">
+        <v>75</v>
+      </c>
+      <c r="L9" t="n">
+        <v>17</v>
+      </c>
+      <c r="N9" t="n">
+        <v>37</v>
+      </c>
+      <c r="O9" t="n">
+        <v>109</v>
+      </c>
+      <c r="P9" t="n">
+        <v>166</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>36</v>
+      </c>
+      <c r="R9" t="n">
+        <v>36</v>
+      </c>
+      <c r="S9" t="n">
+        <v>36</v>
+      </c>
+      <c r="T9" t="n">
+        <v>128</v>
+      </c>
+      <c r="U9" t="n">
+        <v>18</v>
+      </c>
+      <c r="V9" t="n">
+        <v>36</v>
+      </c>
+      <c r="W9" t="n">
+        <v>67</v>
+      </c>
+      <c r="X9" t="n">
+        <v>61</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>93</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>71</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>65</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>33</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>37</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>68</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>45</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>194</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>40</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>64</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>73</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>61</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>36</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>56</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>29</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>137</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>28</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>54</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>37</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>12</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>73</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>notes</t>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Bank Rate</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="1" t="n">
-        <v>35587</v>
-      </c>
       <c r="C11" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="G11" t="n">
         <v>0.0625</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="1" t="n">
-        <v>37152</v>
+        <v>35587</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.0625</v>
+        <v>0.065</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.065</v>
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="n">
-        <v>43901</v>
+      <c r="B13" s="1" t="n">
+        <v>35740</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="H13" t="n">
-        <v>0.0575</v>
+        <v>0.0725</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0.0725</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="1" t="n">
-        <v>43909</v>
+        <v>35803</v>
       </c>
       <c r="C14" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="H14" t="n">
-        <v>0.056</v>
+        <v>0.0725</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Increase</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Increase</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>Increase</t>
+        </is>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0.0725</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="1" t="n">
+        <v>35950</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>Decrease</t>
+        </is>
+      </c>
+      <c r="AK15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0.075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="1" t="n">
+        <v>37105</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="1" t="n">
+        <v>37152</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="1" t="n">
+        <v>39548</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.0475</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="1" t="n">
+        <v>39729</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="1" t="n">
+        <v>39758</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="1" t="n">
+        <v>43314</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AW21" t="n">
+        <v>0.0075</v>
+      </c>
+      <c r="AZ21" t="n">
+        <v>0.0075</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="1" t="n">
+        <v>43901</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AW22" t="n">
+        <v>0.0025</v>
+      </c>
+      <c r="AZ22" t="n">
+        <v>0.0025</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="1" t="n">
+        <v>43909</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AW23" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AZ23" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="1" t="n">
         <v>43916</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="H15" t="n">
-        <v>0.0555</v>
+      <c r="C24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AW24" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="AZ24" t="n">
+        <v>0.001</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="1" t="n">
+        <v>45099</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AW25" t="n">
+        <v>0.045</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="1" t="n">
+        <v>45141</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.055</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="1" t="n">
+        <v>45190</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0.0525</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.055</v>
       </c>
     </row>
   </sheetData>
